--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I212"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,75 +1067,67 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>New or altered vehicle access</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1139,7 +1135,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1166,7 +1162,7 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1185,7 +1181,7 @@
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1193,7 +1189,7 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1212,7 +1208,7 @@
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>New public road</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1220,7 +1216,7 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1239,20 +1235,24 @@
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1262,23 +1262,27 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1293,27 +1297,23 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1337,14 +1337,18 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1354,7 +1358,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1373,18 +1377,18 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1394,51 +1398,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1446,14 +1446,18 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1463,7 +1467,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1482,13 +1486,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1517,13 +1521,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1552,13 +1556,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1587,13 +1591,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1603,7 +1607,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1617,18 +1621,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1674,58 +1674,58 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1749,14 +1749,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1785,18 +1789,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1806,51 +1810,47 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1858,14 +1858,18 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1894,13 +1898,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1910,7 +1914,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1933,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1964,13 +1968,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1999,13 +2003,13 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2015,59 +2019,51 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Protected species impact</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2075,7 +2071,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2094,7 +2090,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2102,7 +2098,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2117,11 +2113,19 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity gain condition applies</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2129,12 +2133,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2144,32 +2148,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2214,24 +2214,24 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2343,24 +2343,28 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2379,18 +2383,18 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2414,23 +2418,23 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2444,28 +2448,24 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2479,19 +2479,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,24 +2510,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2541,14 +2541,18 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2558,32 +2562,32 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2600,17 +2604,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2618,12 +2622,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2633,19 +2637,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2653,17 +2649,17 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2668,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2680,7 +2676,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2695,11 +2691,19 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2707,7 +2711,7 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2717,24 +2721,16 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2742,12 +2738,12 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2761,7 +2757,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2769,12 +2765,12 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2784,24 +2780,36 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2811,16 +2819,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2828,14 +2828,14 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2859,14 +2859,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2974,28 +2974,36 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3005,16 +3013,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -3022,24 +3022,24 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3053,14 +3053,14 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3079,24 +3079,20 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3110,7 +3106,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3118,17 +3114,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3133,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3145,12 +3141,12 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3164,7 +3160,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3172,17 +3168,17 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3187,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3199,7 +3195,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3218,7 +3214,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3226,7 +3222,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3245,7 +3241,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3253,26 +3249,34 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3280,34 +3284,26 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3315,17 +3311,17 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3330,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3342,12 +3338,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3361,7 +3357,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3369,17 +3365,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3384,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3396,7 +3392,7 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3415,7 +3411,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3423,12 +3419,12 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3438,11 +3434,19 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3450,12 +3454,12 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3465,19 +3469,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3485,17 +3481,17 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3500,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3512,17 +3508,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3531,20 +3527,24 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3554,28 +3554,32 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3585,27 +3589,23 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>Substance types[]</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substance type</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3629,24 +3629,24 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance type</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3660,50 +3660,58 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance other</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="2" t="n"/>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3713,16 +3721,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3730,24 +3730,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3761,24 +3761,28 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3797,23 +3801,23 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3832,23 +3836,27 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3880,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3901,77 +3909,69 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="2" t="n"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Building elements[]</t>
@@ -3979,24 +3979,24 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4010,14 +4010,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4041,19 +4041,19 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -4098,19 +4098,15 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4120,7 +4116,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4129,20 +4125,24 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -4152,28 +4152,32 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4183,32 +4187,28 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4227,24 +4227,24 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4258,24 +4258,24 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4289,14 +4289,14 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -4320,14 +4320,14 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -4351,14 +4351,14 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4377,24 +4377,24 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4444,24 +4444,24 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4475,14 +4475,14 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -4528,28 +4528,32 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="2" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4559,19 +4563,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -4579,7 +4575,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4598,25 +4594,33 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4635,13 +4639,13 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4651,7 +4655,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4674,13 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4705,13 +4709,13 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4740,13 +4744,13 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4756,7 +4760,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4770,23 +4774,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4800,24 +4800,20 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -4831,15 +4827,19 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4863,19 +4863,19 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -4889,29 +4889,25 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4916,7 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -4928,12 +4924,12 @@
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -4947,7 +4943,7 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4955,7 +4951,7 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4974,7 +4970,7 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4982,7 +4978,7 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -4997,11 +4993,19 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5009,34 +5013,26 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5044,17 +5040,17 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5059,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5071,7 +5067,7 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -5090,7 +5086,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5098,7 +5094,7 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -5117,7 +5113,7 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5125,7 +5121,7 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -5140,11 +5136,19 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>How waste will be managed on the site</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5152,7 +5156,7 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5162,24 +5166,16 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>How waste will be managed on the site</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5187,12 +5183,12 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves waste management development</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -5206,20 +5202,24 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Type of waste management facility</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -5238,24 +5238,24 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5269,19 +5269,19 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5300,19 +5300,19 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -5331,19 +5331,19 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -5362,19 +5362,19 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5388,24 +5388,24 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5455,14 +5455,14 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -5486,14 +5486,14 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5508,50 +5508,46 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5559,12 +5555,12 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -5578,7 +5574,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5586,17 +5582,17 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5601,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5613,17 +5609,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5628,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5640,17 +5636,17 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5655,7 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>PIP reference</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5667,12 +5663,12 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -5686,7 +5682,7 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Is public service infrastructure</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5694,26 +5690,34 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
@@ -5721,7 +5725,7 @@
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -5736,32 +5740,28 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -5811,19 +5811,23 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -5847,13 +5851,17 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -5887,22 +5895,22 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5926,12 +5934,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -5941,7 +5949,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5960,17 +5968,13 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -5980,7 +5984,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5994,28 +5998,28 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6034,13 +6038,17 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -6074,22 +6082,22 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6121,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -6128,7 +6136,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6147,17 +6155,13 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -6167,7 +6171,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6176,23 +6180,15 @@
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -6202,7 +6198,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6207,7 @@
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr"/>
@@ -6219,7 +6215,7 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -6238,7 +6234,7 @@
       <c r="B181" s="2" t="n"/>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
@@ -6246,7 +6242,7 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -6261,11 +6257,19 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n"/>
-      <c r="B182" s="2" t="n"/>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
@@ -6273,7 +6277,7 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -6288,19 +6292,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr"/>
@@ -6308,39 +6304,51 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="2" t="n"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -6350,16 +6358,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
       <c r="C185" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -6367,19 +6367,19 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -6398,14 +6398,14 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -6429,19 +6429,19 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -6491,14 +6491,14 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -6553,19 +6553,19 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -6584,14 +6584,14 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -6606,50 +6606,46 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n"/>
-      <c r="B193" s="2" t="n"/>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr"/>
       <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr"/>
@@ -6657,12 +6653,12 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -6676,7 +6672,7 @@
       <c r="B195" s="2" t="n"/>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr"/>
@@ -6684,17 +6680,17 @@
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6703,15 +6699,19 @@
       <c r="B196" s="2" t="n"/>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6735,14 +6735,14 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -6766,14 +6766,14 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -6788,28 +6788,32 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n"/>
-      <c r="B199" s="2" t="n"/>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr"/>
       <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -6819,19 +6823,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr"/>
@@ -6839,26 +6835,34 @@
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="2" t="n"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr"/>
@@ -6866,34 +6870,26 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr"/>
@@ -6901,7 +6897,7 @@
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -6916,24 +6912,36 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n"/>
-      <c r="B203" s="2" t="n"/>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -6943,16 +6951,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
       <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -6960,24 +6960,24 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6991,24 +6991,24 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7022,14 +7022,14 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -7053,14 +7053,14 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -7075,28 +7075,32 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n"/>
-      <c r="B208" s="2" t="n"/>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Needs waste storage area</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr"/>
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Does the proposal require a waste storage area</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
@@ -7106,19 +7110,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
+          <t>Waste storage area details</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr"/>
@@ -7126,17 +7122,17 @@
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7141,7 @@
       <c r="B210" s="2" t="n"/>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr"/>
@@ -7153,17 +7149,17 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Does the proposal include separate recycling arrangements</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7168,7 @@
       <c r="B211" s="2" t="n"/>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr"/>
@@ -7180,42 +7176,15 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n"/>
-      <c r="B212" s="2" t="n"/>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr"/>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -7223,68 +7192,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B194:B199"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A160:A166"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A128:A142"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B143:B147"/>
-    <mergeCell ref="A185:A193"/>
-    <mergeCell ref="B51:B64"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="A167:A182"/>
-    <mergeCell ref="B204:B208"/>
-    <mergeCell ref="A143:A147"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A148:A159"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B109:B115"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B160:B166"/>
-    <mergeCell ref="A209:A212"/>
-    <mergeCell ref="B128:B142"/>
-    <mergeCell ref="B185:B193"/>
-    <mergeCell ref="B116:B127"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="B148:B159"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B167:B182"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B37"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B209:B212"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="A204:A208"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="A115:A126"/>
+    <mergeCell ref="B193:B198"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="B64"/>
+    <mergeCell ref="A147:A158"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A203:A207"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="A101:A107"/>
+    <mergeCell ref="A77:A86"/>
+    <mergeCell ref="A184:A192"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A64"/>
+    <mergeCell ref="B108:B114"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="B166:B181"/>
+    <mergeCell ref="A159:A165"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="B50:B63"/>
+    <mergeCell ref="B115:B126"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B77:B86"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B159:B165"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A166:A181"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="B184:B192"/>
+    <mergeCell ref="B147:B158"/>
+    <mergeCell ref="A50:A63"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A29:A36"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="A108:A114"/>
+    <mergeCell ref="B101:B107"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="A127:A141"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -3766,13 +3766,13 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">

--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">

--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I211"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3943,24 +3943,20 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3979,24 +3975,24 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4010,14 +4006,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4041,19 +4037,19 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5143,7 +5139,8 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -5183,7 +5180,7 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5214,7 +5211,7 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5238,24 +5235,24 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5269,24 +5266,24 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5300,24 +5297,24 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5331,24 +5328,24 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5357,24 +5354,24 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5393,14 +5390,14 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -5424,14 +5421,14 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5455,14 +5452,14 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -5477,50 +5474,46 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n"/>
-      <c r="B158" s="2" t="n"/>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
@@ -5528,12 +5521,12 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -5547,7 +5540,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5555,17 +5548,17 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5567,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5582,17 +5575,17 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5594,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5609,17 +5602,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5621,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>PIP reference</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5636,12 +5629,12 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
@@ -5655,7 +5648,7 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Is public service infrastructure</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5663,26 +5656,34 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5690,7 +5691,7 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -5705,32 +5706,28 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -5749,14 +5746,14 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -5780,19 +5777,23 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -5816,13 +5817,17 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -5856,22 +5861,22 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5900,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -5910,7 +5915,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5929,17 +5934,13 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -5949,7 +5950,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5963,28 +5964,28 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6003,13 +6004,17 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -6043,22 +6048,22 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6082,12 +6087,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -6097,7 +6102,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6116,17 +6121,13 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -6136,7 +6137,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6145,23 +6146,15 @@
       <c r="B178" s="2" t="n"/>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -6171,7 +6164,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6173,7 @@
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr"/>
@@ -6188,7 +6181,7 @@
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -6207,7 +6200,7 @@
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr"/>
@@ -6215,7 +6208,7 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -6230,11 +6223,19 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n"/>
-      <c r="B181" s="2" t="n"/>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
@@ -6242,7 +6243,7 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -6257,19 +6258,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
@@ -6277,39 +6270,51 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n"/>
-      <c r="B183" s="2" t="n"/>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -6319,16 +6324,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
       <c r="C184" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -6336,19 +6333,19 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -6367,14 +6364,14 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -6398,19 +6395,19 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -6429,14 +6426,14 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -6460,14 +6457,14 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -6491,14 +6488,14 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -6522,19 +6519,19 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -6553,14 +6550,14 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -6575,50 +6572,46 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n"/>
-      <c r="B192" s="2" t="n"/>
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr"/>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr"/>
@@ -6626,12 +6619,12 @@
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -6645,7 +6638,7 @@
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr"/>
@@ -6653,17 +6646,17 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6672,15 +6665,19 @@
       <c r="B195" s="2" t="n"/>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E195" s="2" t="inlineStr"/>
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -6690,7 +6687,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6704,14 +6701,14 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -6735,14 +6732,14 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -6757,28 +6754,32 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n"/>
-      <c r="B198" s="2" t="n"/>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr"/>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -6788,19 +6789,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr"/>
@@ -6808,26 +6801,34 @@
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n"/>
-      <c r="B200" s="2" t="n"/>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr"/>
@@ -6835,34 +6836,26 @@
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n"/>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr"/>
@@ -6870,7 +6863,7 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -6885,24 +6878,36 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="n"/>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -6912,16 +6917,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n"/>
       <c r="C203" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -6929,24 +6926,24 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6960,24 +6957,24 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6991,14 +6988,14 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -7022,14 +7019,14 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -7044,28 +7041,32 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n"/>
-      <c r="B207" s="2" t="n"/>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Needs waste storage area</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr"/>
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Does the proposal require a waste storage area</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
@@ -7075,19 +7076,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
+          <t>Waste storage area details</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr"/>
@@ -7095,17 +7088,17 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7107,7 @@
       <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr"/>
@@ -7122,17 +7115,17 @@
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Does the proposal include separate recycling arrangements</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7134,7 @@
       <c r="B210" s="2" t="n"/>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr"/>
@@ -7149,42 +7142,15 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n"/>
-      <c r="B211" s="2" t="n"/>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr"/>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -7193,65 +7159,65 @@
   </sheetData>
   <mergeCells count="62">
     <mergeCell ref="B97:B100"/>
+    <mergeCell ref="A158:A164"/>
+    <mergeCell ref="A207:A210"/>
     <mergeCell ref="A115:A126"/>
-    <mergeCell ref="B193:B198"/>
     <mergeCell ref="B65:B67"/>
     <mergeCell ref="B64"/>
-    <mergeCell ref="A147:A158"/>
+    <mergeCell ref="A183:A191"/>
     <mergeCell ref="B68:B70"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A203:A207"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="B147:B157"/>
     <mergeCell ref="B93:B96"/>
     <mergeCell ref="A41:A46"/>
     <mergeCell ref="A68:A70"/>
     <mergeCell ref="B2:B18"/>
     <mergeCell ref="B71:B76"/>
-    <mergeCell ref="A208:A211"/>
     <mergeCell ref="A101:A107"/>
+    <mergeCell ref="B158:B164"/>
     <mergeCell ref="A77:A86"/>
-    <mergeCell ref="A184:A192"/>
+    <mergeCell ref="A198:A199"/>
     <mergeCell ref="A87:A92"/>
     <mergeCell ref="A64"/>
+    <mergeCell ref="A202:A206"/>
     <mergeCell ref="B108:B114"/>
+    <mergeCell ref="A165:A180"/>
+    <mergeCell ref="B183:B191"/>
     <mergeCell ref="B142:B146"/>
-    <mergeCell ref="B166:B181"/>
-    <mergeCell ref="A159:A165"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="A147:A157"/>
+    <mergeCell ref="B181:B182"/>
     <mergeCell ref="B50:B63"/>
     <mergeCell ref="B115:B126"/>
     <mergeCell ref="A142:A146"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="B77:B86"/>
+    <mergeCell ref="A192:A197"/>
+    <mergeCell ref="B198:B199"/>
     <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B201:B202"/>
     <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A200:A201"/>
     <mergeCell ref="A2:A18"/>
     <mergeCell ref="B29:B36"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B165:B180"/>
     <mergeCell ref="B19:B24"/>
-    <mergeCell ref="B159:B165"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A166:A181"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B202:B206"/>
     <mergeCell ref="B127:B141"/>
     <mergeCell ref="A93:A96"/>
-    <mergeCell ref="B184:B192"/>
-    <mergeCell ref="B147:B158"/>
+    <mergeCell ref="B207:B210"/>
     <mergeCell ref="A50:A63"/>
-    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B192:B197"/>
     <mergeCell ref="A29:A36"/>
-    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B200:B201"/>
     <mergeCell ref="B25:B28"/>
     <mergeCell ref="A19:A24"/>
     <mergeCell ref="A108:A114"/>
     <mergeCell ref="B101:B107"/>
-    <mergeCell ref="B199:B200"/>
     <mergeCell ref="B41:B46"/>
     <mergeCell ref="A127:A141"/>
   </mergeCells>

--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,67 +1063,75 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1135,7 +1139,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1154,7 +1158,7 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1162,7 +1166,7 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1181,7 +1185,7 @@
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1189,7 +1193,7 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1208,7 +1212,7 @@
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1216,7 +1220,7 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1235,24 +1239,20 @@
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1262,27 +1262,23 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1297,23 +1293,27 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1337,18 +1337,14 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1358,7 +1354,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1377,18 +1373,18 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1398,47 +1394,51 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1446,18 +1446,14 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1467,7 +1463,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1486,13 +1482,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1521,13 +1517,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1556,13 +1552,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1591,13 +1587,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1607,7 +1603,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1621,14 +1617,18 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1674,58 +1674,58 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1749,18 +1749,14 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1770,7 +1766,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1789,18 +1785,18 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1810,47 +1806,51 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1858,18 +1858,14 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1879,7 +1875,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1898,13 +1894,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1914,7 +1910,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1933,13 +1929,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1968,13 +1964,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2003,13 +1999,13 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2019,51 +2015,59 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2071,7 +2075,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2090,7 +2094,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2098,7 +2102,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2113,19 +2117,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2133,12 +2129,12 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2148,28 +2144,32 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2214,24 +2214,24 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2343,28 +2343,24 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2383,18 +2379,18 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2418,23 +2414,23 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2448,24 +2444,28 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2479,19 +2479,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,24 +2510,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2541,18 +2541,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2562,32 +2558,32 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2604,17 +2600,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2622,12 +2618,12 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2637,11 +2633,19 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2649,17 +2653,17 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2672,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2676,7 +2680,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2691,19 +2695,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2711,7 +2707,7 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2721,16 +2717,24 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2738,12 +2742,12 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2757,7 +2761,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2765,12 +2769,12 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2780,36 +2784,24 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2819,8 +2811,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2828,19 +2828,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2859,19 +2859,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2885,24 +2885,24 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2921,19 +2921,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2952,19 +2952,19 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -2974,36 +2974,28 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3013,8 +3005,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -3022,24 +3022,24 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3053,14 +3053,14 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3079,20 +3079,24 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3106,7 +3110,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3114,17 +3118,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3137,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3141,12 +3145,12 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3160,7 +3164,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3168,17 +3172,17 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3191,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3195,7 +3199,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3222,7 +3226,7 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3241,7 +3245,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3249,34 +3253,26 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3284,26 +3280,34 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3311,17 +3315,17 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3334,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3338,12 +3342,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3357,7 +3361,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3365,17 +3369,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3388,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3392,7 +3396,7 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3411,7 +3415,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3419,12 +3423,12 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3434,19 +3438,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3454,12 +3450,12 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3469,11 +3465,19 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3481,17 +3485,17 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3504,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3508,17 +3512,17 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3527,24 +3531,20 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Connect to drainage system</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3554,32 +3554,28 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3589,23 +3585,27 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substance type</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3629,24 +3629,24 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance other</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3660,58 +3660,50 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3721,8 +3713,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3730,24 +3730,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3761,28 +3761,24 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3801,23 +3797,23 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3836,27 +3832,23 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3880,12 +3872,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3909,49 +3901,53 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Closing time</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>Hours not known</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Applicant states they do not know the hours of operation</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Proposal material details</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3961,33 +3957,37 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -4006,24 +4006,24 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4037,14 +4037,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -4068,19 +4068,19 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4094,15 +4094,19 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4121,24 +4125,20 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -4148,32 +4148,28 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4183,28 +4179,32 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4223,24 +4223,24 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4254,24 +4254,24 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4285,19 +4285,19 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -4316,19 +4316,19 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -4347,19 +4347,19 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -4373,24 +4373,24 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -4409,24 +4409,24 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4440,24 +4440,24 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4471,19 +4471,19 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4502,19 +4502,19 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -4524,32 +4524,28 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4559,11 +4555,19 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -4571,7 +4575,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4590,33 +4594,25 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4635,13 +4631,13 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4651,7 +4647,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4666,13 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4705,13 +4701,13 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4740,13 +4736,13 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4756,7 +4752,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4770,19 +4766,23 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4796,20 +4796,24 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -4823,29 +4827,25 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4854,29 +4854,25 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4885,25 +4881,29 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4912,25 +4912,29 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4943,7 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4947,7 +4951,7 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4957,7 +4961,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4970,7 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4974,34 +4978,26 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5009,12 +5005,12 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -5024,11 +5020,19 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="2" t="n"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5036,17 +5040,17 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5059,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5063,7 +5067,7 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -5082,7 +5086,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5090,12 +5094,12 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -5109,7 +5113,7 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5117,12 +5121,12 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5132,20 +5136,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5153,7 +5148,7 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5163,16 +5158,25 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5180,12 +5184,12 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -5199,24 +5203,20 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -5235,19 +5235,19 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5297,19 +5297,19 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -5328,19 +5328,19 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -5354,29 +5354,29 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5390,19 +5390,19 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -5421,19 +5421,19 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -5452,19 +5452,19 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -5474,46 +5474,50 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
@@ -5521,12 +5525,12 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -5540,7 +5544,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5548,17 +5552,17 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5571,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5575,17 +5579,17 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5598,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5602,17 +5606,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5625,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5629,12 +5633,12 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -5910,7 +5914,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -5945,7 +5949,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -6058,7 +6062,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -6097,7 +6101,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -6132,7 +6136,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -6159,7 +6163,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -6186,7 +6190,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -6213,7 +6217,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -6248,7 +6252,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -6407,7 +6411,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -6438,7 +6442,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -6469,7 +6473,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -6526,7 +6530,7 @@
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -6969,7 +6973,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -7000,7 +7004,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -7031,7 +7035,7 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
@@ -7158,68 +7162,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="A158:A164"/>
     <mergeCell ref="A207:A210"/>
-    <mergeCell ref="A115:A126"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="B64"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="B159:B164"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
     <mergeCell ref="A183:A191"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B147:B157"/>
-    <mergeCell ref="B93:B96"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="A101:A107"/>
-    <mergeCell ref="B158:B164"/>
-    <mergeCell ref="A77:A86"/>
+    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A128:A142"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="B143:B147"/>
     <mergeCell ref="A198:A199"/>
-    <mergeCell ref="A87:A92"/>
-    <mergeCell ref="A64"/>
+    <mergeCell ref="B51:B64"/>
     <mergeCell ref="A202:A206"/>
-    <mergeCell ref="B108:B114"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="B66:B68"/>
     <mergeCell ref="A165:A180"/>
     <mergeCell ref="B183:B191"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A147:A157"/>
+    <mergeCell ref="A143:A147"/>
+    <mergeCell ref="B42:B47"/>
     <mergeCell ref="B181:B182"/>
-    <mergeCell ref="B50:B63"/>
-    <mergeCell ref="B115:B126"/>
-    <mergeCell ref="A142:A146"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B77:B86"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A78:A87"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B88:B93"/>
     <mergeCell ref="A192:A197"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A51:A64"/>
     <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="B109:B115"/>
     <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A69:A71"/>
     <mergeCell ref="B165:B180"/>
-    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B128:B142"/>
     <mergeCell ref="A181:A182"/>
     <mergeCell ref="B202:B206"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="B116:B127"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A159:A164"/>
     <mergeCell ref="B207:B210"/>
-    <mergeCell ref="A50:A63"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B78:B87"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A148:A158"/>
     <mergeCell ref="B192:B197"/>
-    <mergeCell ref="A29:A36"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B102:B108"/>
     <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A108:A114"/>
-    <mergeCell ref="B101:B107"/>
-    <mergeCell ref="B41:B46"/>
-    <mergeCell ref="A127:A141"/>
+    <mergeCell ref="A116:A127"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/full-planning-permission-full.xlsx
+++ b/generated/spreadsheet/full-planning-permission-full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I210"/>
+  <dimension ref="A1:I213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1587,13 +1587,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1622,13 +1626,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1652,14 +1660,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1683,19 +1699,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1705,58 +1721,58 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1780,18 +1796,14 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1801,7 +1813,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,18 +1832,18 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1841,47 +1853,51 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1889,18 +1905,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1910,7 +1922,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1929,13 +1941,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1945,7 +1957,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1964,13 +1976,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1999,13 +2011,13 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2034,58 +2046,66 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2094,34 +2114,54 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2129,7 +2169,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2144,19 +2184,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2164,12 +2196,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2183,19 +2215,15 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Geological features impact</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2210,28 +2238,32 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2245,24 +2277,24 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2276,24 +2308,24 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2312,24 +2344,24 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2375,24 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2374,28 +2406,24 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2409,28 +2437,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2473,23 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2479,19 +2503,23 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2510,24 +2538,28 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2541,24 +2573,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2572,23 +2604,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2598,27 +2626,23 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2628,37 +2652,37 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2668,11 +2692,19 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2680,7 +2712,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2690,16 +2722,24 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2707,31 +2747,23 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2742,7 +2774,7 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2752,7 +2784,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2793,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2769,26 +2801,34 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2796,12 +2836,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2811,36 +2851,24 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2854,24 +2882,20 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2881,8 +2905,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2890,19 +2922,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2916,19 +2948,19 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2947,24 +2979,24 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -2983,19 +3015,19 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3005,36 +3037,28 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3048,35 +3072,43 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -3084,19 +3116,19 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3110,25 +3142,29 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3137,15 +3173,19 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3155,7 +3195,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3204,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3172,17 +3212,17 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3231,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3199,17 +3239,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3258,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3226,17 +3266,17 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3285,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3253,7 +3293,7 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3272,7 +3312,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3280,34 +3320,26 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3315,7 +3347,7 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3334,7 +3366,7 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -3342,12 +3374,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3357,11 +3389,19 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3369,17 +3409,17 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3428,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3396,17 +3436,17 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3455,7 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3423,17 +3463,17 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3482,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3450,12 +3490,12 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3465,19 +3505,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3485,7 +3517,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3504,7 +3536,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3512,7 +3544,7 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3522,16 +3554,24 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3539,7 +3579,7 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3558,46 +3598,34 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Foul sewage disposal types[]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3605,12 +3633,12 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3624,24 +3652,24 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance type</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3651,33 +3679,37 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substance other</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3691,19 +3723,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3713,41 +3745,33 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3756,35 +3780,43 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="2" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3792,18 +3824,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3827,23 +3855,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3867,22 +3891,18 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3906,27 +3926,23 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3940,54 +3956,66 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -4001,60 +4029,64 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4068,24 +4100,24 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4099,19 +4131,19 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -4125,25 +4157,29 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4152,46 +4188,38 @@
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -4199,7 +4227,7 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4218,24 +4246,24 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -4245,33 +4273,37 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="2" t="n"/>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4285,19 +4317,19 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -4316,24 +4348,24 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4347,14 +4379,14 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4378,14 +4410,14 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4404,24 +4436,24 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4435,29 +4467,29 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4471,19 +4503,19 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4502,24 +4534,24 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4533,14 +4565,14 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -4555,32 +4587,28 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Total rooms proposed</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -4594,20 +4622,24 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -4617,37 +4649,37 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="2" t="n"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4656,28 +4688,20 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -4701,13 +4725,13 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4717,7 +4741,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4736,13 +4760,13 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -4771,13 +4795,13 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -4787,7 +4811,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4801,24 +4825,32 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4827,20 +4859,32 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4854,15 +4898,27 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4881,29 +4937,29 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4912,29 +4968,25 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4995,7 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4951,7 +5003,7 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4961,7 +5013,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4970,20 +5022,24 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -4997,15 +5053,19 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -5020,19 +5080,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5040,12 +5092,12 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -5059,7 +5111,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5067,17 +5119,17 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5138,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5094,26 +5146,34 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5121,17 +5181,17 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5200,7 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5148,7 +5208,7 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5163,20 +5223,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5184,7 +5235,7 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5194,7 +5245,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5254,7 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -5211,17 +5262,17 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5230,55 +5281,56 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Site activity details</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5292,24 +5344,20 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Unit type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -5328,19 +5376,19 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -5359,19 +5407,19 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5385,29 +5433,29 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5464,19 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5438,7 +5486,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5447,29 +5495,29 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5483,14 +5531,14 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5505,37 +5553,33 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5544,25 +5588,29 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5571,20 +5619,24 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5594,11 +5646,19 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5606,12 +5666,12 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
@@ -5625,7 +5685,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5633,17 +5693,17 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5712,7 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5660,34 +5720,26 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5695,7 +5747,7 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -5714,29 +5766,25 @@
       <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Tenure type</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5745,24 +5793,20 @@
       <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Is public service infrastructure</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -5772,27 +5816,27 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n"/>
-      <c r="B168" s="2" t="n"/>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -5816,27 +5860,19 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -5855,32 +5891,24 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5899,22 +5927,18 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -5938,23 +5962,27 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5968,28 +5996,32 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6035,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -6013,17 +6045,17 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -6042,22 +6074,18 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -6086,22 +6114,18 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -6125,23 +6149,27 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6178,27 @@
       <c r="B178" s="2" t="n"/>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr"/>
-      <c r="E178" s="2" t="inlineStr"/>
-      <c r="F178" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -6168,7 +6208,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6177,15 +6217,27 @@
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="2" t="inlineStr"/>
-      <c r="F179" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -6204,15 +6256,23 @@
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -6222,24 +6282,16 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Total existing units</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
@@ -6247,12 +6299,12 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -6266,7 +6318,7 @@
       <c r="B182" s="2" t="n"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
@@ -6274,87 +6326,79 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="2" t="n"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6363,24 +6407,20 @@
       <c r="B185" s="2" t="n"/>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -6390,8 +6430,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n"/>
-      <c r="B186" s="2" t="n"/>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -6399,24 +6447,24 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6430,24 +6478,28 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6461,19 +6513,23 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -6492,19 +6548,23 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -6523,14 +6583,18 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -6554,19 +6618,19 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -6576,37 +6640,33 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6615,25 +6675,29 @@
       <c r="B193" s="2" t="n"/>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6642,20 +6706,24 @@
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E194" s="2" t="inlineStr"/>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -6665,28 +6733,32 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n"/>
-      <c r="B195" s="2" t="n"/>
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr"/>
       <c r="E195" s="2" t="inlineStr"/>
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -6700,24 +6772,20 @@
       <c r="B196" s="2" t="n"/>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr"/>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -6731,19 +6799,15 @@
       <c r="B197" s="2" t="n"/>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -6753,37 +6817,33 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -6797,15 +6857,19 @@
       <c r="B199" s="2" t="n"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -6815,37 +6879,33 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E200" s="2" t="inlineStr"/>
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -6855,11 +6915,19 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="2" t="n"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr"/>
@@ -6867,7 +6935,7 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -6882,72 +6950,64 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Parking space type</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr"/>
       <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n"/>
-      <c r="B203" s="2" t="n"/>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle type other</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr"/>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6956,24 +7016,20 @@
       <c r="B204" s="2" t="n"/>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Total existing</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr"/>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -6983,8 +7039,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n"/>
-      <c r="B205" s="2" t="n"/>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+        </is>
+      </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
           <t>Parking spaces[]</t>
@@ -6992,19 +7056,19 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Parking space type</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -7023,54 +7087,50 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Difference in spaces</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n"/>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Total existing</t>
+        </is>
+      </c>
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
@@ -7084,25 +7144,29 @@
       <c r="B208" s="2" t="n"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Total proposed</t>
+        </is>
+      </c>
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7111,20 +7175,24 @@
       <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Difference in spaces</t>
+        </is>
+      </c>
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
@@ -7134,11 +7202,19 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n"/>
-      <c r="B210" s="2" t="n"/>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements details</t>
+          <t>Needs waste storage area</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr"/>
@@ -7146,15 +7222,96 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
+          <t>Does the proposal require a waste storage area</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal include separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements details</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
           <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -7162,68 +7319,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A207:A210"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="B159:B164"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A183:A191"/>
-    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="B53:B66"/>
+    <mergeCell ref="B118:B129"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="B205:B209"/>
+    <mergeCell ref="B168:B183"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A128:A142"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B143:B147"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B51:B64"/>
-    <mergeCell ref="A202:A206"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="A165:A180"/>
-    <mergeCell ref="B183:B191"/>
-    <mergeCell ref="A143:A147"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="A192:A197"/>
+    <mergeCell ref="A104:A110"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A151:A161"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A67"/>
+    <mergeCell ref="A53:A66"/>
+    <mergeCell ref="B151:B161"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="A162:A167"/>
+    <mergeCell ref="B195:B200"/>
+    <mergeCell ref="A130:A145"/>
+    <mergeCell ref="B186:B194"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B210:B213"/>
+    <mergeCell ref="A111:A117"/>
+    <mergeCell ref="B30:B38"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A74:A79"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B109:B115"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B165:B180"/>
-    <mergeCell ref="B128:B142"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B202:B206"/>
-    <mergeCell ref="B116:B127"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A159:A164"/>
-    <mergeCell ref="B207:B210"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A148:A158"/>
-    <mergeCell ref="B192:B197"/>
+    <mergeCell ref="B104:B110"/>
+    <mergeCell ref="A118:A129"/>
+    <mergeCell ref="B162:B167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A210:A213"/>
+    <mergeCell ref="A186:A194"/>
+    <mergeCell ref="A195:A200"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A80:A89"/>
+    <mergeCell ref="B130:B145"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B67"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="B43:B49"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A205:A209"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="A201:A202"/>
     <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A168:A183"/>
+    <mergeCell ref="B184:B185"/>
     <mergeCell ref="B20:B25"/>
-    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A39:A42"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A146:A150"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="B80:B89"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
